--- a/result/ADAM10_LUAD_Tables.xlsx
+++ b/result/ADAM10_LUAD_Tables.xlsx
@@ -962,7 +962,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>EGFR_Mut_Binary</t>
+          <t>EGFRExpression</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>0.130</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>0.006</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.011</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.837</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-0.001</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.865</t>
+          <t>0.983</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>0.011</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.810</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>-0.123</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.007</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.024</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.595</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.061</t>
         </is>
       </c>
     </row>
@@ -1634,14 +1634,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.177</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EGFR_Mut_Binary</t>
+          <t>EGFRExpression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1651,37 +1651,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>0.130</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>-0.123</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.024</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.061</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1699,37 +1699,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.837</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.865</t>
+          <t>0.983</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.595</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>

--- a/result/ADAM10_LUAD_Tables.xlsx
+++ b/result/ADAM10_LUAD_Tables.xlsx
@@ -10,8 +10,9 @@
     <sheet name="Table 1 (Chi-square)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 3.1 (Cox)_stage_continuous" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 4 (Multivariate OLS)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -962,7 +963,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>EGFRExpression</t>
+          <t>EGFR_Mut_Binary</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1015,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.130</t>
+          <t>-0.002</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1059,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.978</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1111,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.042</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1155,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>0.611</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1207,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.012</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1251,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>0.865</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1303,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-0.102</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1347,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.810</t>
+          <t>0.139</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1399,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.123</t>
+          <t>0.008</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1443,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.904</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1495,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.024</t>
+          <t>-0.050</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1539,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>0.469</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1591,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.107</t>
         </is>
       </c>
     </row>
@@ -1634,14 +1635,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.122</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EGFRExpression</t>
+          <t>EGFR_Mut_Binary</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1651,37 +1652,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.130</t>
+          <t>-0.002</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.042</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-0.102</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.123</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.024</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.107</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1699,37 +1700,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.978</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>0.611</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>0.865</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.810</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.904</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>0.469</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1745,7 +1746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1778,21 +1779,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ageG</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.453</v>
+        <v>1.013</v>
       </c>
       <c r="C2" t="n">
-        <v>1.002</v>
+        <v>0.993</v>
       </c>
       <c r="D2" t="n">
-        <v>2.109</v>
+        <v>1.033</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>0.205</t>
         </is>
       </c>
     </row>
@@ -1803,101 +1804,122 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.993</v>
+        <v>0.991</v>
       </c>
       <c r="D3" t="n">
         <v>1.007</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>0.771</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
+          <t>ADAM10group_Low</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.497</v>
+        <v>0.743</v>
       </c>
       <c r="C4" t="n">
-        <v>1.256</v>
+        <v>0.503</v>
       </c>
       <c r="D4" t="n">
-        <v>1.784</v>
+        <v>1.096</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.134</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADAM10group_High</t>
+          <t>gender_MALE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.236</v>
+        <v>1.163</v>
       </c>
       <c r="C5" t="n">
-        <v>0.643</v>
+        <v>0.773</v>
       </c>
       <c r="D5" t="n">
-        <v>2.376</v>
+        <v>1.75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>0.469</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADAM10group_Low</t>
+          <t>pathologic_stage_2.0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.887</v>
+        <v>2.026</v>
       </c>
       <c r="C6" t="n">
-        <v>0.46</v>
+        <v>1.255</v>
       </c>
       <c r="D6" t="n">
-        <v>1.71</v>
+        <v>3.271</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.720</t>
+          <t>0.004</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_MALE</t>
+          <t>pathologic_stage_3.0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.262</v>
+        <v>2.733</v>
       </c>
       <c r="C7" t="n">
-        <v>0.863</v>
+        <v>1.649</v>
       </c>
       <c r="D7" t="n">
-        <v>1.845</v>
+        <v>4.529</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.230</t>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>pathologic_stage_4.0</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.772</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.856</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.008</t>
         </is>
       </c>
     </row>
@@ -1912,18 +1934,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Clinical Variable</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Coefficient</t>
+          <t>Hazard Ratio (HR)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1943,902 +1965,109 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <f>== [ Model: Pathologic Stage ] ===</f>
-        <v/>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.179</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ADAM10expression</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.743</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ADAM10expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_stage)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.814</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.0264</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>ADAM10group_Low</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.102</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2.4711e-01</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>983.8768</v>
-      </c>
-      <c r="C8" t="n">
-        <v>594.2524</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1373.5013</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>36.5889</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-83.6467</v>
-      </c>
-      <c r="D9" t="n">
-        <v>156.8246</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.550</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>95.0689</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-47.398</v>
-      </c>
-      <c r="D10" t="n">
-        <v>237.5358</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.190</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>-39.8924</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-202.333</v>
-      </c>
-      <c r="D11" t="n">
-        <v>122.5481</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.629</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>11.0321</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-269.7202</v>
-      </c>
-      <c r="D12" t="n">
-        <v>291.7844</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.938</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>6.3123</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.5097</v>
-      </c>
-      <c r="D13" t="n">
-        <v>12.115</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.033</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.3487</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-1.8185</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.516</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.752</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <f>== [ Model: Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ADAM10expression</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ADAM10expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_T)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.0330</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.2778e-01</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>953.0533</v>
-      </c>
-      <c r="C22" t="n">
-        <v>560.7707</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1345.3359</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>17.3447</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-103.4504</v>
-      </c>
-      <c r="D23" t="n">
-        <v>138.1398</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>119.002</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-9.827</v>
-      </c>
-      <c r="D24" t="n">
-        <v>247.831</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0.070</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>102.9747</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-110.8036</v>
-      </c>
-      <c r="D25" t="n">
-        <v>316.753</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0.344</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>297.2967</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-6.6935</v>
-      </c>
-      <c r="D26" t="n">
-        <v>601.287</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0.055</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>5.9605</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.2252</v>
-      </c>
-      <c r="D27" t="n">
-        <v>11.6957</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.042</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0.2803</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-1.8831</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2.4437</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.799</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <f>== [ Model: Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ADAM10expression</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ADAM10expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_N)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>0.0215</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3.8443e-01</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1014.5671</v>
-      </c>
-      <c r="C36" t="n">
-        <v>622.5453</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1406.589</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>44.4795</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-76.1495</v>
-      </c>
-      <c r="D37" t="n">
-        <v>165.1086</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.469</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>30.7639</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-120.6687</v>
-      </c>
-      <c r="D38" t="n">
-        <v>182.1965</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.690</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>-70.9391</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-246.1249</v>
-      </c>
-      <c r="D39" t="n">
-        <v>104.2468</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.426</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>-111.4269</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-829.5839</v>
-      </c>
-      <c r="D40" t="n">
-        <v>606.7301</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.760</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>6.1852</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.3227</v>
-      </c>
-      <c r="D41" t="n">
-        <v>12.0477</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0.039</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0.2596</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-1.9373</v>
-      </c>
-      <c r="D42" t="n">
-        <v>2.4566</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.816</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <f>== [ Model: Pathologic M ] ===</f>
-        <v/>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>ADAM10expression</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>ADAM10expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_M)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0.0220</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>3.2615e-01</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1020.6067</v>
-      </c>
-      <c r="C50" t="n">
-        <v>578.4468000000001</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1462.7666</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>52.0381</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-86.9824</v>
-      </c>
-      <c r="D51" t="n">
-        <v>191.0586</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.461</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>C(pathologic_M)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>-37.1131</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-313.9649</v>
-      </c>
-      <c r="D52" t="n">
-        <v>239.7386</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.792</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>6.5426</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.1343</v>
-      </c>
-      <c r="D53" t="n">
-        <v>13.2196</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.055</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-2.496</v>
-      </c>
-      <c r="D54" t="n">
-        <v>2.646</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0.954</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+          <t>gender_MALE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.734</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.465</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2851,6 +2080,1117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>== [ Model: Base Model (No Stage) ] ===</f>
+        <v/>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ADAM10expression</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADAM10expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.0144</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2.2999e-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1060.6191</v>
+      </c>
+      <c r="C8" t="n">
+        <v>679.2886</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1441.9497</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>40.2928</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-77.5834</v>
+      </c>
+      <c r="D9" t="n">
+        <v>158.169</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.502</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.402</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.3395</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1434</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.065</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.8568</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.4643</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.782</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <f>== [ Model: Base + Pathologic Stage ] ===</f>
+        <v/>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ADAM10expression</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ADAM10expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.0264</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.4711e-01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>983.8768</v>
+      </c>
+      <c r="C19" t="n">
+        <v>594.2524</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1373.5013</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>36.5889</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-83.6467</v>
+      </c>
+      <c r="D20" t="n">
+        <v>156.8246</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.550</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>95.0689</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-47.398</v>
+      </c>
+      <c r="D21" t="n">
+        <v>237.5358</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.190</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-39.8924</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-202.333</v>
+      </c>
+      <c r="D22" t="n">
+        <v>122.5481</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.629</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>11.0321</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-269.7202</v>
+      </c>
+      <c r="D23" t="n">
+        <v>291.7844</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.938</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6.3123</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.5097</v>
+      </c>
+      <c r="D24" t="n">
+        <v>12.115</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0.033</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.8185</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0.752</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ADAM10expression</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ADAM10expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.0330</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1.2778e-01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>953.0533</v>
+      </c>
+      <c r="C33" t="n">
+        <v>560.7707</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1345.3359</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>17.3447</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-103.4504</v>
+      </c>
+      <c r="D34" t="n">
+        <v>138.1398</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>119.002</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-9.827</v>
+      </c>
+      <c r="D35" t="n">
+        <v>247.831</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.070</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>102.9747</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-110.8036</v>
+      </c>
+      <c r="D36" t="n">
+        <v>316.753</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.344</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>297.2967</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-6.6935</v>
+      </c>
+      <c r="D37" t="n">
+        <v>601.287</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.055</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5.9605</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.2252</v>
+      </c>
+      <c r="D38" t="n">
+        <v>11.6957</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.042</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-1.8831</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.4437</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.799</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ADAM10expression</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ADAM10expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0.0215</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>3.8443e-01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1014.5671</v>
+      </c>
+      <c r="C47" t="n">
+        <v>622.5453</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1406.589</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>44.4795</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-76.1495</v>
+      </c>
+      <c r="D48" t="n">
+        <v>165.1086</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.469</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>30.7639</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-120.6687</v>
+      </c>
+      <c r="D49" t="n">
+        <v>182.1965</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.690</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>-70.9391</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-246.1249</v>
+      </c>
+      <c r="D50" t="n">
+        <v>104.2468</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.426</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>-111.4269</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-829.5839</v>
+      </c>
+      <c r="D51" t="n">
+        <v>606.7301</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.760</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>6.1852</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="D52" t="n">
+        <v>12.0477</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.039</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.2596</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-1.9373</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.4566</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0.816</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <f>== [ Model: Base + Pathologic M ] ===</f>
+        <v/>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ADAM10expression</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ADAM10expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0.0220</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>3.2615e-01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1020.6067</v>
+      </c>
+      <c r="C61" t="n">
+        <v>578.4468000000001</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1462.7666</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>52.0381</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-86.9824</v>
+      </c>
+      <c r="D62" t="n">
+        <v>191.0586</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0.461</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C(pathologic_M)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>-37.1131</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-313.9649</v>
+      </c>
+      <c r="D63" t="n">
+        <v>239.7386</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0.792</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>6.5426</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.1343</v>
+      </c>
+      <c r="D64" t="n">
+        <v>13.2196</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0.055</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-2.496</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2.646</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0.954</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2899,12 +3239,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.937</t>
+          <t>6.738</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.009</t>
         </is>
       </c>
     </row>

--- a/result/ADAM10_LUAD_Tables.xlsx
+++ b/result/ADAM10_LUAD_Tables.xlsx
@@ -3239,12 +3239,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.738</t>
+          <t>5.937</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.015</t>
         </is>
       </c>
     </row>

--- a/result/ADAM10_LUAD_Tables.xlsx
+++ b/result/ADAM10_LUAD_Tables.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,18 +439,17 @@
           <t>Clinical Characteristics</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -465,7 +464,6 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -474,17 +472,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="C3" t="n">
-        <v>93</v>
-      </c>
-      <c r="D3" t="n">
         <v>125</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.253</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.397</t>
         </is>
       </c>
     </row>
@@ -495,15 +490,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="C4" t="n">
-        <v>105</v>
-      </c>
-      <c r="D4" t="n">
         <v>120</v>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -514,7 +506,6 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -523,17 +514,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>103</v>
       </c>
       <c r="C6" t="n">
-        <v>103</v>
-      </c>
-      <c r="D6" t="n">
         <v>141</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.284</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.245</t>
         </is>
       </c>
     </row>
@@ -544,15 +532,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>95</v>
-      </c>
-      <c r="D7" t="n">
         <v>104</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -563,7 +548,6 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -572,17 +556,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="C9" t="n">
-        <v>95</v>
-      </c>
-      <c r="D9" t="n">
         <v>145</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.287</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.116</t>
         </is>
       </c>
     </row>
@@ -593,15 +574,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>51</v>
-      </c>
-      <c r="D10" t="n">
         <v>55</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -610,15 +588,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>36</v>
-      </c>
-      <c r="D11" t="n">
         <v>33</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -627,15 +602,12 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
-      </c>
-      <c r="D12" t="n">
         <v>9</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -646,7 +618,6 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -655,17 +626,14 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="C14" t="n">
-        <v>131</v>
-      </c>
-      <c r="D14" t="n">
         <v>162</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.471</t>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.269</t>
         </is>
       </c>
     </row>
@@ -676,15 +644,12 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
-      </c>
-      <c r="D15" t="n">
         <v>9</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -695,7 +660,6 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -704,17 +668,14 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="C17" t="n">
-        <v>122</v>
-      </c>
-      <c r="D17" t="n">
         <v>167</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0.537</t>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.475</t>
         </is>
       </c>
     </row>
@@ -725,15 +686,12 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C18" t="n">
-        <v>37</v>
-      </c>
-      <c r="D18" t="n">
         <v>47</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -742,15 +700,12 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
-      </c>
-      <c r="D19" t="n">
         <v>27</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -759,15 +714,12 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -778,7 +730,6 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -787,17 +738,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="C22" t="n">
-        <v>61</v>
-      </c>
-      <c r="D22" t="n">
         <v>93</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.056</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.106</t>
         </is>
       </c>
     </row>
@@ -808,15 +756,12 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="C23" t="n">
-        <v>100</v>
-      </c>
-      <c r="D23" t="n">
         <v>127</v>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -825,15 +770,12 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>23</v>
-      </c>
-      <c r="D24" t="n">
         <v>19</v>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -842,15 +784,12 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
-      </c>
-      <c r="D25" t="n">
         <v>6</v>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -861,7 +800,6 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -870,17 +808,14 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="C27" t="n">
-        <v>67</v>
-      </c>
-      <c r="D27" t="n">
         <v>77</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.867</t>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.596</t>
         </is>
       </c>
     </row>
@@ -891,15 +826,12 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="C28" t="n">
-        <v>132</v>
-      </c>
-      <c r="D28" t="n">
         <v>169</v>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/result/ADAM10_LUAD_Tables.xlsx
+++ b/result/ADAM10_LUAD_Tables.xlsx
@@ -875,27 +875,27 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>EGFRExpression</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>KrasExpression</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>TP53Expression</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ALKExpression</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>BRAFExpression</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>EGFR_Mut_Binary</t>
         </is>
       </c>
     </row>
@@ -927,27 +927,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0.130</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>0.146</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>-0.156</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>-0.048</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.140</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-0.002</t>
         </is>
       </c>
     </row>
@@ -971,27 +971,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>0.006</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>0.002</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>0.310</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.003</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.978</t>
         </is>
       </c>
     </row>
@@ -1023,27 +1023,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>-0.039</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.046</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>-0.016</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.042</t>
         </is>
       </c>
     </row>
@@ -1067,27 +1067,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0.837</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>0.482</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>0.408</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.859</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>0.774</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.611</t>
         </is>
       </c>
     </row>
@@ -1119,27 +1119,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>-0.001</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>-0.022</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>0.072</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>-0.048</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>-0.050</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.012</t>
         </is>
       </c>
     </row>
@@ -1163,34 +1163,34 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
+          <t>0.983</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>0.624</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>0.112</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>0.291</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>0.265</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.865</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KrasExpression</t>
+          <t>EGFRExpression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1200,17 +1200,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.130</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1220,22 +1220,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.057</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.123</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.080</t>
+          <t>-0.024</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>0.061</t>
         </is>
       </c>
     </row>
@@ -1248,45 +1248,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>0.837</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>0.983</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.595</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.177</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>KrasExpression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,42 +1296,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.156</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>-0.039</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>-0.022</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>-0.057</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.067</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.080</t>
         </is>
       </c>
     </row>
@@ -1344,45 +1344,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.482</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.624</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.940</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.078</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALKExpression</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1392,42 +1392,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.048</t>
+          <t>-0.156</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.048</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.123</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.067</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.040</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.003</t>
         </is>
       </c>
     </row>
@@ -1440,45 +1440,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.310</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.940</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRAFExpression</t>
+          <t>ALKExpression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.140</t>
+          <t>-0.048</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.048</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.080</t>
+          <t>-0.024</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>0.067</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>-0.040</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0.107</t>
         </is>
       </c>
     </row>
@@ -1536,45 +1536,45 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.310</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.595</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.940</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.372</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EGFR_Mut_Binary</t>
+          <t>BRAFExpression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1584,37 +1584,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>0.140</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>-0.016</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>0.061</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.080</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1632,37 +1632,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.774</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.865</t>
+          <t>0.265</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.940</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1678,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,15 +1694,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1717,13 +1712,12 @@
       <c r="B2" t="n">
         <v>1.013</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.993</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.033</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.993-1.033</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.205</t>
         </is>
@@ -1738,13 +1732,12 @@
       <c r="B3" t="n">
         <v>0.999</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.007</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.991-1.007</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.771</t>
         </is>
@@ -1759,13 +1752,12 @@
       <c r="B4" t="n">
         <v>0.743</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.096</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.503-1.096</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.134</t>
         </is>
@@ -1780,13 +1772,12 @@
       <c r="B5" t="n">
         <v>1.163</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.773-1.750</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.469</t>
         </is>
@@ -1801,13 +1792,12 @@
       <c r="B6" t="n">
         <v>2.026</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.255</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3.271</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.255-3.271</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.004</t>
         </is>
@@ -1822,13 +1812,12 @@
       <c r="B7" t="n">
         <v>2.733</v>
       </c>
-      <c r="C7" t="n">
-        <v>1.649</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4.529</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1.649-4.529</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -1843,13 +1832,12 @@
       <c r="B8" t="n">
         <v>2.772</v>
       </c>
-      <c r="C8" t="n">
-        <v>1.312</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5.856</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.312-5.856</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>0.008</t>
         </is>
@@ -1866,7 +1854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1882,15 +1870,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1905,13 +1888,12 @@
       <c r="B2" t="n">
         <v>1.014</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.994</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.034</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.994-1.034</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.179</t>
         </is>
@@ -1926,13 +1908,12 @@
       <c r="B3" t="n">
         <v>0.999</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.006</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.991-1.006</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.743</t>
         </is>
@@ -1947,13 +1928,12 @@
       <c r="B4" t="n">
         <v>1.504</v>
       </c>
-      <c r="C4" t="n">
-        <v>1.247</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.814</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.247-1.814</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -1968,13 +1948,12 @@
       <c r="B5" t="n">
         <v>0.724</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.066</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.491-1.066</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.102</t>
         </is>
@@ -1989,13 +1968,12 @@
       <c r="B6" t="n">
         <v>1.161</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.734</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.778-1.734</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.465</t>
         </is>
@@ -2012,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2028,15 +2006,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -2050,7 +2023,6 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2065,7 +2037,6 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2080,7 +2051,6 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2095,7 +2065,6 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2110,7 +2079,6 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2121,7 +2089,6 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2130,15 +2097,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1060.6191</v>
-      </c>
-      <c r="C8" t="n">
-        <v>679.2886</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1441.9497</v>
-      </c>
-      <c r="E8" t="inlineStr">
+        <v>1060.619</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>679.289-1441.95</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2151,15 +2117,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40.2928</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-77.5834</v>
-      </c>
-      <c r="D9" t="n">
-        <v>158.169</v>
-      </c>
-      <c r="E9" t="inlineStr">
+        <v>40.293</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-77.583-158.169</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>0.502</t>
         </is>
@@ -2174,13 +2139,12 @@
       <c r="B10" t="n">
         <v>5.402</v>
       </c>
-      <c r="C10" t="n">
-        <v>-0.3395</v>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1434</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-0.339-11.143</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>0.065</t>
         </is>
@@ -2193,15 +2157,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3037</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.8568</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.4643</v>
-      </c>
-      <c r="E11" t="inlineStr">
+        <v>0.304</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-1.857-2.464</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>0.782</t>
         </is>
@@ -2212,7 +2175,6 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13">
@@ -2222,7 +2184,6 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2237,7 +2198,6 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2252,7 +2212,6 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2267,7 +2226,6 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2282,7 +2240,6 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2293,7 +2250,6 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2302,15 +2258,14 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>983.8768</v>
-      </c>
-      <c r="C19" t="n">
-        <v>594.2524</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1373.5013</v>
-      </c>
-      <c r="E19" t="inlineStr">
+        <v>983.877</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>594.252-1373.501</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2323,15 +2278,14 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>36.5889</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-83.6467</v>
-      </c>
-      <c r="D20" t="n">
-        <v>156.8246</v>
-      </c>
-      <c r="E20" t="inlineStr">
+        <v>36.589</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-83.647-156.825</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>0.550</t>
         </is>
@@ -2344,15 +2298,14 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>95.0689</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-47.398</v>
-      </c>
-      <c r="D21" t="n">
-        <v>237.5358</v>
-      </c>
-      <c r="E21" t="inlineStr">
+        <v>95.069</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-47.398-237.536</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>0.190</t>
         </is>
@@ -2365,15 +2318,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-39.8924</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-202.333</v>
-      </c>
-      <c r="D22" t="n">
-        <v>122.5481</v>
-      </c>
-      <c r="E22" t="inlineStr">
+        <v>-39.892</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-202.333-122.548</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>0.629</t>
         </is>
@@ -2386,15 +2338,14 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11.0321</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-269.7202</v>
-      </c>
-      <c r="D23" t="n">
-        <v>291.7844</v>
-      </c>
-      <c r="E23" t="inlineStr">
+        <v>11.032</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-269.72-291.784</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>0.938</t>
         </is>
@@ -2407,15 +2358,14 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6.3123</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.5097</v>
-      </c>
-      <c r="D24" t="n">
-        <v>12.115</v>
-      </c>
-      <c r="E24" t="inlineStr">
+        <v>6.312</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.51-12.115</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>0.033</t>
         </is>
@@ -2428,15 +2378,14 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3487</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-1.8185</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2.516</v>
-      </c>
-      <c r="E25" t="inlineStr">
+        <v>0.349</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-1.818-2.516</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>0.752</t>
         </is>
@@ -2447,7 +2396,6 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27">
@@ -2457,7 +2405,6 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2472,7 +2419,6 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2487,7 +2433,6 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2502,7 +2447,6 @@
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2517,7 +2461,6 @@
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2528,7 +2471,6 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2537,15 +2479,14 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>953.0533</v>
-      </c>
-      <c r="C33" t="n">
-        <v>560.7707</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1345.3359</v>
-      </c>
-      <c r="E33" t="inlineStr">
+        <v>953.053</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>560.771-1345.336</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2558,15 +2499,14 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.3447</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-103.4504</v>
-      </c>
-      <c r="D34" t="n">
-        <v>138.1398</v>
-      </c>
-      <c r="E34" t="inlineStr">
+        <v>17.345</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-103.45-138.14</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>0.778</t>
         </is>
@@ -2581,13 +2521,12 @@
       <c r="B35" t="n">
         <v>119.002</v>
       </c>
-      <c r="C35" t="n">
-        <v>-9.827</v>
-      </c>
-      <c r="D35" t="n">
-        <v>247.831</v>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-9.827-247.831</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>0.070</t>
         </is>
@@ -2600,15 +2539,14 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>102.9747</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-110.8036</v>
-      </c>
-      <c r="D36" t="n">
-        <v>316.753</v>
-      </c>
-      <c r="E36" t="inlineStr">
+        <v>102.975</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-110.804-316.753</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>0.344</t>
         </is>
@@ -2621,15 +2559,14 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>297.2967</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-6.6935</v>
-      </c>
-      <c r="D37" t="n">
-        <v>601.287</v>
-      </c>
-      <c r="E37" t="inlineStr">
+        <v>297.297</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-6.694-601.287</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>0.055</t>
         </is>
@@ -2642,15 +2579,14 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5.9605</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.2252</v>
-      </c>
-      <c r="D38" t="n">
-        <v>11.6957</v>
-      </c>
-      <c r="E38" t="inlineStr">
+        <v>5.96</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0.225-11.696</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>0.042</t>
         </is>
@@ -2663,15 +2599,14 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.2803</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-1.8831</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2.4437</v>
-      </c>
-      <c r="E39" t="inlineStr">
+        <v>0.28</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>-1.883-2.444</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>0.799</t>
         </is>
@@ -2682,7 +2617,6 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41">
@@ -2692,7 +2626,6 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2707,7 +2640,6 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2722,7 +2654,6 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2737,7 +2668,6 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2752,7 +2682,6 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2763,7 +2692,6 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2772,15 +2700,14 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1014.5671</v>
-      </c>
-      <c r="C47" t="n">
-        <v>622.5453</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1406.589</v>
-      </c>
-      <c r="E47" t="inlineStr">
+        <v>1014.567</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>622.545-1406.589</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2793,15 +2720,14 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>44.4795</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-76.1495</v>
-      </c>
-      <c r="D48" t="n">
-        <v>165.1086</v>
-      </c>
-      <c r="E48" t="inlineStr">
+        <v>44.48</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>-76.149-165.109</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>0.469</t>
         </is>
@@ -2814,15 +2740,14 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>30.7639</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-120.6687</v>
-      </c>
-      <c r="D49" t="n">
-        <v>182.1965</v>
-      </c>
-      <c r="E49" t="inlineStr">
+        <v>30.764</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>-120.669-182.197</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>0.690</t>
         </is>
@@ -2835,15 +2760,14 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-70.9391</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-246.1249</v>
-      </c>
-      <c r="D50" t="n">
-        <v>104.2468</v>
-      </c>
-      <c r="E50" t="inlineStr">
+        <v>-70.93899999999999</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>-246.125-104.247</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>0.426</t>
         </is>
@@ -2856,15 +2780,14 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-111.4269</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-829.5839</v>
-      </c>
-      <c r="D51" t="n">
-        <v>606.7301</v>
-      </c>
-      <c r="E51" t="inlineStr">
+        <v>-111.427</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-829.584-606.73</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>0.760</t>
         </is>
@@ -2877,15 +2800,14 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6.1852</v>
-      </c>
-      <c r="C52" t="n">
-        <v>0.3227</v>
-      </c>
-      <c r="D52" t="n">
-        <v>12.0477</v>
-      </c>
-      <c r="E52" t="inlineStr">
+        <v>6.185</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.323-12.048</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>0.039</t>
         </is>
@@ -2898,15 +2820,14 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.2596</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-1.9373</v>
-      </c>
-      <c r="D53" t="n">
-        <v>2.4566</v>
-      </c>
-      <c r="E53" t="inlineStr">
+        <v>0.26</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>-1.937-2.457</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>0.816</t>
         </is>
@@ -2917,7 +2838,6 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55">
@@ -2927,7 +2847,6 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2942,7 +2861,6 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2957,7 +2875,6 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2972,7 +2889,6 @@
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2987,7 +2903,6 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2998,7 +2913,6 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3007,15 +2921,14 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1020.6067</v>
-      </c>
-      <c r="C61" t="n">
-        <v>578.4468000000001</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1462.7666</v>
-      </c>
-      <c r="E61" t="inlineStr">
+        <v>1020.607</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>578.447-1462.767</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -3028,15 +2941,14 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>52.0381</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-86.9824</v>
-      </c>
-      <c r="D62" t="n">
-        <v>191.0586</v>
-      </c>
-      <c r="E62" t="inlineStr">
+        <v>52.038</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-86.982-191.059</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>0.461</t>
         </is>
@@ -3049,15 +2961,14 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-37.1131</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-313.9649</v>
-      </c>
-      <c r="D63" t="n">
-        <v>239.7386</v>
-      </c>
-      <c r="E63" t="inlineStr">
+        <v>-37.113</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-313.965-239.739</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>0.792</t>
         </is>
@@ -3070,15 +2981,14 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>6.5426</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.1343</v>
-      </c>
-      <c r="D64" t="n">
-        <v>13.2196</v>
-      </c>
-      <c r="E64" t="inlineStr">
+        <v>6.543</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-0.134-13.22</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>0.055</t>
         </is>
@@ -3093,13 +3003,12 @@
       <c r="B65" t="n">
         <v>0.075</v>
       </c>
-      <c r="C65" t="n">
-        <v>-2.496</v>
-      </c>
-      <c r="D65" t="n">
-        <v>2.646</v>
-      </c>
-      <c r="E65" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-2.496-2.646</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>0.954</t>
         </is>
@@ -3110,7 +3019,6 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
